--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-servicerequest-common.xlsx
@@ -4247,7 +4247,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
